--- a/branches/fix/go-publish-bootstrap/ValueSet-mii-vs-biobank-biosafety-level-snomedct.xlsx
+++ b/branches/fix/go-publish-bootstrap/ValueSet-mii-vs-biobank-biosafety-level-snomedct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:07:49+00:00</t>
+    <t>2026-09-11T10:33:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
